--- a/Result/profitability/2323.xlsx
+++ b/Result/profitability/2323.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06000000000000002</v>
+        <v>0.1975</v>
       </c>
       <c r="N2" t="n">
-        <v>21.04</v>
+        <v>21.565</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.79</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07625000000000001</v>
+        <v>0.17875</v>
       </c>
       <c r="N3" t="n">
-        <v>16.42375</v>
+        <v>16.82375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07375000000000001</v>
+        <v>0.2275</v>
       </c>
       <c r="N4" t="n">
-        <v>12.94875</v>
+        <v>13.23875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001249999999999994</v>
+        <v>0.1075</v>
       </c>
       <c r="N5" t="n">
-        <v>10.19875</v>
+        <v>10.06625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1075</v>
+        <v>-0.03625000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>7.01125</v>
+        <v>7.274999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22875</v>
+        <v>-0.205</v>
       </c>
       <c r="N7" t="n">
-        <v>4.56125</v>
+        <v>4.80875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4</v>
+        <v>-0.17375</v>
       </c>
       <c r="N8" t="n">
-        <v>2.505</v>
+        <v>2.382499999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E75" t="n">
+        <v>478</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>58</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1714</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1772</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1522</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.92875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.414634146341463</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9800000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0371493555724034</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8499999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.060000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.04006046863189727</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
